--- a/output/pdf_financials_xlsx/BCBN.xlsx
+++ b/output/pdf_financials_xlsx/BCBN.xlsx
@@ -642,10 +642,10 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.148</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.252</v>
       </c>
     </row>
     <row r="13">
@@ -926,10 +926,10 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-26.7</v>
+        <v>-26.848</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.524</v>
+        <v>0.272</v>
       </c>
     </row>
     <row r="28">
@@ -962,10 +962,10 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-26.649</v>
+        <v>-26.797</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.577</v>
+        <v>0.325</v>
       </c>
     </row>
     <row r="30">
@@ -6704,7 +6704,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -6737,7 +6737,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">

--- a/output/pdf_financials_xlsx/BCBN.xlsx
+++ b/output/pdf_financials_xlsx/BCBN.xlsx
@@ -732,10 +732,10 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>-2.205</v>
+        <v>2.205</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-0.279</v>
+        <v>0.279</v>
       </c>
     </row>
     <row r="18">
@@ -2441,13 +2441,13 @@
         </is>
       </c>
       <c r="B121" s="3" t="n">
-        <v>0</v>
+        <v>-1.889462</v>
       </c>
       <c r="C121" s="3" t="n">
-        <v>0</v>
+        <v>-2.939</v>
       </c>
       <c r="D121" s="3" t="n">
-        <v>0</v>
+        <v>-2.98</v>
       </c>
     </row>
     <row r="122">
@@ -5516,7 +5516,11 @@
           <t>Repurchase of shares 11</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E93" s="5" t="n">
         <v>-1.889462</v>
       </c>
@@ -6863,7 +6867,11 @@
           <t>Income tax recovery (expense) 10</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr"/>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E136" t="inlineStr">
         <is>
           <t>-</t>
